--- a/questionnaire_templates/021_email_and_narrative_writing_quiz--questionnaire_templates.xlsx
+++ b/questionnaire_templates/021_email_and_narrative_writing_quiz--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
